--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.33" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.33" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.33.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.33.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0033.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0033.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.33.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.33" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.33" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,17 +422,17 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="49" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -591,7 +591,11 @@
       </c>
       <c r="D2" s="1" t="inlineStr"/>
       <c r="E2" s="1" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>L30: candidate OCR token mismatch vs other OCR: "paintiff's" vs "plaintiff’s" :: against youasthe Court shall just upon the paintiff's</t>
+        </is>
+      </c>
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr">
@@ -601,16 +605,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: with these words.â€”" A Defendant is to answer or demur,</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L70: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Plaintiffâ€™s Solicitor.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]26 THE WRIT.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]26 THE WRIT.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 26</t>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,19 +676,15 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Service of the Subp Ã¦ ena is by delivering a copy to the</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: against you as the Court shall think just upon the plaintiffâ€™s</t>
-        </is>
-      </c>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: at Osgoode Hall in the City of Toronto ； and you do</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L10: isolated marker/symbol line :: 185</t>
+          <t>L3: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -727,19 +731,15 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L131: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: with these words.â€”" A Defendant is to answer or demur,</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: own showingâ€”(where the defendant is to be served out</t>
-        </is>
-      </c>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L18: isolated marker/symbol line :: 1</t>
+          <t>L10: isolated marker/symbol line :: 185</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -786,19 +786,15 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L159: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Service of the Subp Ã¦ ena is by delivering a copy to the</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the jurisdiction, add the following words)â€”without</t>
-        </is>
-      </c>
+          <t>L97: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: at Osgoode Hall in the City of Toronto ； and you do</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 4</t>
+          <t>L18: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -844,16 +840,12 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: memorandum, with these words.â€”" A Defendant is to answer or demur,</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 26</t>
+          <t>L53: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -900,7 +892,7 @@
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 185</t>
+          <t>L65: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -927,7 +919,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -947,7 +939,7 @@
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 1</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+7535 CJK UNIFIED IDEOGRAPH-7535 | isolated marker/symbol line :: 电</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -994,7 +986,7 @@
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: 238;</t>
+          <t>L77: isolated marker/symbol line :: 185</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr"/>
@@ -1022,7 +1014,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1037,7 +1029,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L134: symbol-only separator/garbage line :: 391;</t>
+          <t>L90: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1065,7 +1057,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1080,7 +1072,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 4</t>
+          <t>L124: symbol-only separator/garbage line :: 238;</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1103,7 +1095,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1123,7 +1115,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: X</t>
+          <t>L134: symbol-only separator/garbage line :: 391;</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1166,7 +1158,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L164: isolated marker/symbol line :: T</t>
+          <t>L147: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1207,7 +1199,11 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L157: isolated marker/symbol line :: X</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
@@ -1246,7 +1242,11 @@
       <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
-      <c r="N15" s="1" t="inlineStr"/>
+      <c r="N15" s="1" t="inlineStr">
+        <is>
+          <t>L164: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
       <c r="O15" s="1" t="inlineStr"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
